--- a/A/chrVII:347117-396704_69_finemapping.xlsx
+++ b/A/chrVII:347117-396704_69_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2403" uniqueCount="2403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2395" uniqueCount="2395">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -1844,13 +1844,13 @@
     <t xml:space="preserve">Biosynthesis of secondary metabolites - Saccharomyces cerevisiae (budding yeast)</t>
   </si>
   <si>
-    <t xml:space="preserve">9/23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301/1898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YDL182W/YDR032C/YHR007C/YIL094C/YJL167W/YLR153C/YML008C/YPL117C/YPL028W</t>
+    <t xml:space="preserve">10/23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309/1898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YDL182W/YDR032C/YHR007C/YIL094C/YJL167W/YLR153C/YML008C/YPL117C/YPL028W/YPR069C</t>
   </si>
   <si>
     <t xml:space="preserve">Amino acid metabolism</t>
@@ -6245,19 +6245,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -6792,21 +6783,6 @@
   </si>
   <si>
     <t xml:space="preserve">SUL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -7659,48 +7635,42 @@
         <v>2073</v>
       </c>
       <c r="Z1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA1" t="s">
         <v>2074</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>2075</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>2076</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
         <v>2077</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>2078</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>2079</v>
       </c>
-      <c r="AF1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>2080</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>2081</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>2082</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>2083</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -7754,62 +7724,60 @@
         <v>378078</v>
       </c>
       <c r="U2" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="V2" t="n">
         <v>552604</v>
       </c>
       <c r="W2" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z2" t="n">
         <v>-0.274421210280019</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.0292238373601634</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>2086</v>
       </c>
       <c r="AD2" t="s">
         <v>18</v>
       </c>
       <c r="AE2" t="s">
-        <v>2089</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>2089</v>
-      </c>
-      <c r="AH2" t="n">
+        <v>2086</v>
+      </c>
+      <c r="AF2" t="n">
         <v>4</v>
       </c>
-      <c r="AI2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>2090</v>
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>2087</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>2091</v>
+        <v>2088</v>
       </c>
       <c r="D3" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
       <c r="E3" t="n">
         <v>378078</v>
@@ -7860,59 +7828,57 @@
         <v>383573</v>
       </c>
       <c r="U3" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="V3" t="n">
         <v>388822</v>
       </c>
       <c r="W3" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-0.146785980629911</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.0155646611477282</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>2091</v>
       </c>
       <c r="AD3" t="s">
         <v>18</v>
       </c>
       <c r="AE3" t="s">
-        <v>2094</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>2094</v>
-      </c>
-      <c r="AH3" t="n">
+        <v>2091</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" t="b">
+      <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>2095</v>
+      <c r="AH3" t="s">
+        <v>2092</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
       <c r="D4" t="s">
         <v>57</v>
@@ -7966,62 +7932,60 @@
         <v>364650</v>
       </c>
       <c r="U4" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
       <c r="V4" t="n">
         <v>139364</v>
       </c>
       <c r="W4" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-0.190245329263061</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.0308722456846609</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>2095</v>
       </c>
       <c r="AD4" t="s">
         <v>18</v>
       </c>
       <c r="AE4" t="s">
-        <v>2098</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>2098</v>
-      </c>
-      <c r="AH4" t="n">
+        <v>2095</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0</v>
       </c>
-      <c r="AI4" t="b">
+      <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>2099</v>
+      <c r="AH4" t="s">
+        <v>2096</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
       <c r="D5" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
       <c r="E5" t="n">
         <v>371489</v>
@@ -8072,62 +8036,60 @@
         <v>374227</v>
       </c>
       <c r="U5" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
       <c r="V5" t="n">
         <v>85676</v>
       </c>
       <c r="W5" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z5" t="n">
         <v>0.0864592313981924</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.0149845671252752</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>2100</v>
       </c>
       <c r="AD5" t="s">
         <v>18</v>
       </c>
       <c r="AE5" t="s">
-        <v>2103</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>2103</v>
-      </c>
-      <c r="AH5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" t="b">
+      <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>2104</v>
+      <c r="AH5" t="s">
+        <v>2101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
       <c r="D6" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="E6" t="n">
         <v>357041</v>
@@ -8178,59 +8140,57 @@
         <v>362321</v>
       </c>
       <c r="U6" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
       <c r="V6" t="n">
         <v>186397</v>
       </c>
       <c r="W6" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.114851704107345</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.0199982844649614</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>2105</v>
       </c>
       <c r="AD6" t="s">
         <v>18</v>
       </c>
       <c r="AE6" t="s">
-        <v>2108</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>2108</v>
-      </c>
-      <c r="AH6" t="n">
+        <v>2105</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0</v>
       </c>
-      <c r="AI6" t="b">
+      <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="s">
-        <v>2109</v>
+      <c r="AH6" t="s">
+        <v>2106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>2110</v>
+        <v>2107</v>
       </c>
       <c r="D7" t="s">
         <v>57</v>
@@ -8284,62 +8244,60 @@
         <v>364650</v>
       </c>
       <c r="U7" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="V7" t="n">
         <v>1410272</v>
       </c>
       <c r="W7" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-0.166136220200906</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.0308865303172886</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>2109</v>
       </c>
       <c r="AD7" t="s">
         <v>18</v>
       </c>
       <c r="AE7" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AH7" t="n">
+        <v>2109</v>
+      </c>
+      <c r="AF7" t="n">
         <v>0</v>
       </c>
-      <c r="AI7" t="b">
+      <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>2110</v>
+      <c r="AH7" t="s">
+        <v>2107</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
       <c r="D8" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
       <c r="E8" t="n">
         <v>348923</v>
@@ -8390,62 +8348,60 @@
         <v>357841</v>
       </c>
       <c r="U8" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="V8" t="n">
         <v>240259</v>
       </c>
       <c r="W8" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z8" t="n">
         <v>-0.148224920669503</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.0286539498055274</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>2109</v>
       </c>
       <c r="AD8" t="s">
         <v>18</v>
       </c>
       <c r="AE8" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AH8" t="n">
+        <v>2109</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0</v>
       </c>
-      <c r="AI8" t="b">
+      <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>2113</v>
+      <c r="AH8" t="s">
+        <v>2110</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
       <c r="D9" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="E9" t="n">
         <v>357041</v>
@@ -8496,59 +8452,57 @@
         <v>362321</v>
       </c>
       <c r="U9" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="V9" t="n">
         <v>986779</v>
       </c>
       <c r="W9" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z9" t="n">
         <v>0.384214730214136</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.0823975683173414</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>2114</v>
       </c>
       <c r="AD9" t="s">
         <v>18</v>
       </c>
       <c r="AE9" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>2118</v>
+        <v>2114</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>2115</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
       <c r="D10" t="s">
         <v>64</v>
@@ -8602,59 +8556,57 @@
         <v>371489</v>
       </c>
       <c r="U10" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="V10" t="n">
         <v>368781</v>
       </c>
       <c r="W10" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.0480680672924472</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.0104882039512528</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>2086</v>
       </c>
       <c r="AD10" t="s">
         <v>18</v>
       </c>
       <c r="AE10" t="s">
-        <v>2089</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>2089</v>
-      </c>
-      <c r="AH10" t="n">
+        <v>2086</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" t="b">
+      <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>2120</v>
+      <c r="AH10" t="s">
+        <v>2117</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
       <c r="D11" t="s">
         <v>64</v>
@@ -8708,59 +8660,57 @@
         <v>371489</v>
       </c>
       <c r="U11" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
       <c r="V11" t="n">
         <v>142174</v>
       </c>
       <c r="W11" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z11" t="n">
         <v>-0.049406612245034</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.0108956245635348</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>2095</v>
       </c>
       <c r="AD11" t="s">
         <v>18</v>
       </c>
       <c r="AE11" t="s">
-        <v>2098</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>2098</v>
-      </c>
-      <c r="AH11" t="n">
+        <v>2095</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" t="b">
+      <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="s">
-        <v>2122</v>
+      <c r="AH11" t="s">
+        <v>2119</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="D12" t="s">
         <v>57</v>
@@ -8814,62 +8764,60 @@
         <v>364650</v>
       </c>
       <c r="U12" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
       <c r="V12" t="n">
         <v>418537</v>
       </c>
       <c r="W12" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z12" t="n">
         <v>-0.115156406121443</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.0278969930477665</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>2122</v>
       </c>
       <c r="AD12" t="s">
         <v>18</v>
       </c>
       <c r="AE12" t="s">
-        <v>2125</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>2125</v>
-      </c>
-      <c r="AH12" t="n">
+        <v>2122</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0</v>
       </c>
-      <c r="AI12" t="b">
+      <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="s">
-        <v>2123</v>
+      <c r="AH12" t="s">
+        <v>2120</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
       <c r="D13" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="E13" t="n">
         <v>378078</v>
@@ -8920,59 +8868,57 @@
         <v>385519</v>
       </c>
       <c r="U13" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="V13" t="n">
         <v>645950</v>
       </c>
       <c r="W13" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-0.0753368993515335</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.019362410838212</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>2126</v>
       </c>
       <c r="AD13" t="s">
         <v>18</v>
       </c>
       <c r="AE13" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AH13" t="n">
+        <v>2126</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0</v>
       </c>
-      <c r="AI13" t="b">
+      <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>2130</v>
+      <c r="AH13" t="s">
+        <v>2127</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
       <c r="D14" t="s">
         <v>64</v>
@@ -9026,62 +8972,60 @@
         <v>371489</v>
       </c>
       <c r="U14" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="V14" t="n">
         <v>169650</v>
       </c>
       <c r="W14" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z14" t="n">
         <v>0.755785460530833</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.190763653830598</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>2126</v>
       </c>
       <c r="AD14" t="s">
         <v>18</v>
       </c>
       <c r="AE14" t="s">
+        <v>2126</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="s">
         <v>2129</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>2132</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
       <c r="D15" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
       <c r="E15" t="n">
         <v>357041</v>
@@ -9132,62 +9076,60 @@
         <v>372717</v>
       </c>
       <c r="U15" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="V15" t="n">
         <v>774752</v>
       </c>
       <c r="W15" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z15" t="n">
         <v>0.108811622275046</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.0284125854808005</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>2091</v>
       </c>
       <c r="AD15" t="s">
         <v>18</v>
       </c>
       <c r="AE15" t="s">
-        <v>2094</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>2094</v>
-      </c>
-      <c r="AH15" t="n">
+        <v>2091</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" t="b">
+      <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AJ15" t="s">
-        <v>2135</v>
+      <c r="AH15" t="s">
+        <v>2132</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
       <c r="D16" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E16" t="n">
         <v>385519</v>
@@ -9238,62 +9180,60 @@
         <v>392315</v>
       </c>
       <c r="U16" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="V16" t="n">
         <v>1434924</v>
       </c>
       <c r="W16" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>2138</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>2135</v>
+      </c>
+      <c r="Z16" t="n">
         <v>0.254316309953883</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0679600871565995</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>2109</v>
       </c>
       <c r="AD16" t="s">
         <v>18</v>
       </c>
       <c r="AE16" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AH16" t="n">
+        <v>2109</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0</v>
       </c>
-      <c r="AI16" t="b">
+      <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="s">
-        <v>2139</v>
+      <c r="AH16" t="s">
+        <v>2136</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>2140</v>
+        <v>2137</v>
       </c>
       <c r="D17" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="E17" t="n">
         <v>357041</v>
@@ -9344,62 +9284,60 @@
         <v>385519</v>
       </c>
       <c r="U17" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="V17" t="n">
         <v>517958</v>
       </c>
       <c r="W17" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z17" t="n">
         <v>0.0814743099782663</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.0238492690884966</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>2139</v>
       </c>
       <c r="AD17" t="s">
         <v>18</v>
       </c>
       <c r="AE17" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AH17" t="n">
+        <v>2139</v>
+      </c>
+      <c r="AF17" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" t="b">
+      <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="s">
-        <v>2143</v>
+      <c r="AH17" t="s">
+        <v>2140</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
       <c r="D18" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="E18" t="n">
         <v>348923</v>
@@ -9450,59 +9388,57 @@
         <v>385519</v>
       </c>
       <c r="U18" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="V18" t="n">
         <v>497370</v>
       </c>
       <c r="W18" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z18" t="n">
         <v>-0.163979974257551</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.0444871547458907</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>2143</v>
       </c>
       <c r="AD18" t="s">
         <v>18</v>
       </c>
       <c r="AE18" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AH18" t="n">
+        <v>2143</v>
+      </c>
+      <c r="AF18" t="n">
         <v>0</v>
       </c>
-      <c r="AI18" t="b">
+      <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="s">
-        <v>2147</v>
+      <c r="AH18" t="s">
+        <v>2144</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -9556,62 +9492,60 @@
         <v>378078</v>
       </c>
       <c r="U19" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="V19" t="n">
         <v>202555</v>
       </c>
       <c r="W19" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z19" t="n">
         <v>-0.117640804483904</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.0334114552426285</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>2091</v>
       </c>
       <c r="AD19" t="s">
         <v>18</v>
       </c>
       <c r="AE19" t="s">
-        <v>2094</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>2094</v>
-      </c>
-      <c r="AH19" t="n">
+        <v>2091</v>
+      </c>
+      <c r="AF19" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" t="b">
+      <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>2149</v>
+      <c r="AH19" t="s">
+        <v>2146</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
       <c r="D20" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
       <c r="E20" t="n">
         <v>357041</v>
@@ -9662,62 +9596,60 @@
         <v>374227</v>
       </c>
       <c r="U20" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="V20" t="n">
         <v>877005</v>
       </c>
       <c r="W20" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z20" t="n">
         <v>-0.0833709967432467</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.0227047139700246</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>2114</v>
       </c>
       <c r="AD20" t="s">
         <v>18</v>
       </c>
       <c r="AE20" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AH20" t="n">
+        <v>2114</v>
+      </c>
+      <c r="AF20" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" t="b">
+      <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="s">
-        <v>2151</v>
+      <c r="AH20" t="s">
+        <v>2148</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="D21" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
       <c r="E21" t="n">
         <v>357041</v>
@@ -9768,62 +9700,60 @@
         <v>383573</v>
       </c>
       <c r="U21" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="V21" t="n">
         <v>503947</v>
       </c>
       <c r="W21" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z21" t="n">
         <v>-0.0792309110245418</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.0223107535824863</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>2109</v>
       </c>
       <c r="AD21" t="s">
         <v>18</v>
       </c>
       <c r="AE21" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AH21" t="n">
+        <v>2109</v>
+      </c>
+      <c r="AF21" t="n">
         <v>0</v>
       </c>
-      <c r="AI21" t="b">
+      <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="s">
-        <v>2153</v>
+      <c r="AH21" t="s">
+        <v>2150</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="D22" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="E22" t="n">
         <v>357041</v>
@@ -9874,62 +9804,60 @@
         <v>362321</v>
       </c>
       <c r="U22" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="V22" t="n">
         <v>416667</v>
       </c>
       <c r="W22" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.192765748479474</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.0590860079271939</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>2139</v>
       </c>
       <c r="AD22" t="s">
         <v>18</v>
       </c>
       <c r="AE22" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AH22" t="n">
+        <v>2139</v>
+      </c>
+      <c r="AF22" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" t="b">
+      <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="s">
-        <v>2155</v>
+      <c r="AH22" t="s">
+        <v>2152</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
       <c r="D23" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
       <c r="E23" t="n">
         <v>386608</v>
@@ -9980,62 +9908,60 @@
         <v>396062</v>
       </c>
       <c r="U23" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="V23" t="n">
         <v>126862</v>
       </c>
       <c r="W23" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>2138</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>2135</v>
+      </c>
+      <c r="Z23" t="n">
         <v>0.407659416651615</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.121727436764952</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>2114</v>
       </c>
       <c r="AD23" t="s">
         <v>18</v>
       </c>
       <c r="AE23" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AH23" t="n">
+        <v>2114</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" t="b">
+      <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="s">
-        <v>2158</v>
+      <c r="AH23" t="s">
+        <v>2155</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>2159</v>
+        <v>2156</v>
       </c>
       <c r="D24" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="E24" t="n">
         <v>334704</v>
@@ -10086,62 +10012,60 @@
         <v>357041</v>
       </c>
       <c r="U24" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="V24" t="n">
         <v>470987</v>
       </c>
       <c r="W24" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="Y24" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.117025508954311</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AA24" t="n">
         <v>0.0382667465492242</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>2159</v>
       </c>
       <c r="AD24" t="s">
         <v>18</v>
       </c>
       <c r="AE24" t="s">
-        <v>2162</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>2162</v>
-      </c>
-      <c r="AH24" t="n">
+        <v>2159</v>
+      </c>
+      <c r="AF24" t="n">
         <v>0</v>
       </c>
-      <c r="AI24" t="b">
+      <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="s">
-        <v>2163</v>
+      <c r="AH24" t="s">
+        <v>2160</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
       <c r="D25" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="E25" t="n">
         <v>371489</v>
@@ -10192,62 +10116,60 @@
         <v>385519</v>
       </c>
       <c r="U25" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="V25" t="n">
         <v>66142</v>
       </c>
       <c r="W25" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
       </c>
-      <c r="Y25"/>
-      <c r="Z25"/>
-      <c r="AA25" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="Y25" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z25" t="n">
         <v>-0.100800178550837</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AA25" t="n">
         <v>0.0319719751806283</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>2143</v>
       </c>
       <c r="AD25" t="s">
         <v>18</v>
       </c>
       <c r="AE25" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AH25" t="n">
+        <v>2143</v>
+      </c>
+      <c r="AF25" t="n">
         <v>0</v>
       </c>
-      <c r="AI25" t="b">
+      <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="s">
-        <v>2165</v>
+      <c r="AH25" t="s">
+        <v>2162</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B26" t="s">
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="D26" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="E26" t="n">
         <v>383573</v>
@@ -10298,59 +10220,57 @@
         <v>385519</v>
       </c>
       <c r="U26" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="V26" t="n">
         <v>18968</v>
       </c>
       <c r="W26" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
       </c>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="Y26" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z26" t="n">
         <v>-0.15802204362653</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AA26" t="n">
         <v>0.0475648003918624</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>2143</v>
       </c>
       <c r="AD26" t="s">
         <v>18</v>
       </c>
       <c r="AE26" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AH26" t="n">
+        <v>2143</v>
+      </c>
+      <c r="AF26" t="n">
         <v>0</v>
       </c>
-      <c r="AI26" t="b">
+      <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="s">
-        <v>2167</v>
+      <c r="AH26" t="s">
+        <v>2164</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="D27" t="s">
         <v>57</v>
@@ -10404,62 +10324,60 @@
         <v>364650</v>
       </c>
       <c r="U27" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="V27" t="n">
         <v>105014</v>
       </c>
       <c r="W27" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
       </c>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AA27" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="Y27" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z27" t="n">
         <v>0.0728296642934081</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AA27" t="n">
         <v>0.0227803680768178</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>2159</v>
       </c>
       <c r="AD27" t="s">
         <v>18</v>
       </c>
       <c r="AE27" t="s">
-        <v>2162</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>2162</v>
-      </c>
-      <c r="AH27" t="n">
+        <v>2159</v>
+      </c>
+      <c r="AF27" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" t="b">
+      <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="s">
-        <v>2169</v>
+      <c r="AH27" t="s">
+        <v>2166</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
       <c r="D28" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
       <c r="E28" t="n">
         <v>371489</v>
@@ -10510,62 +10428,60 @@
         <v>383573</v>
       </c>
       <c r="U28" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="V28" t="n">
         <v>971688</v>
       </c>
       <c r="W28" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
       </c>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AA28" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="Y28" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z28" t="n">
         <v>-0.13211545873426</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AA28" t="n">
         <v>0.044570655766665</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>2109</v>
       </c>
       <c r="AD28" t="s">
         <v>18</v>
       </c>
       <c r="AE28" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>2171</v>
+        <v>2109</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>2168</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
       <c r="D29" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="E29" t="n">
         <v>345331</v>
@@ -10616,62 +10532,60 @@
         <v>385041</v>
       </c>
       <c r="U29" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="V29" t="n">
         <v>95445</v>
       </c>
       <c r="W29" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
       </c>
-      <c r="Y29"/>
-      <c r="Z29"/>
-      <c r="AA29" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="Y29" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z29" t="n">
         <v>-0.0754066084609646</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AA29" t="n">
         <v>0.0246952767691538</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>2086</v>
       </c>
       <c r="AD29" t="s">
         <v>18</v>
       </c>
       <c r="AE29" t="s">
-        <v>2089</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>2089</v>
-      </c>
-      <c r="AH29" t="n">
+        <v>2086</v>
+      </c>
+      <c r="AF29" t="n">
         <v>0</v>
       </c>
-      <c r="AI29" t="b">
+      <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="s">
-        <v>2174</v>
+      <c r="AH29" t="s">
+        <v>2171</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B30" t="s">
         <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
       <c r="D30" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="E30" t="n">
         <v>376112</v>
@@ -10722,59 +10636,57 @@
         <v>385519</v>
       </c>
       <c r="U30" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
       <c r="V30" t="n">
         <v>635146</v>
       </c>
       <c r="W30" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
       </c>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AA30" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="Y30" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z30" t="n">
         <v>-0.0926249520024525</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AA30" t="n">
         <v>0.0303297808691478</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>2122</v>
       </c>
       <c r="AD30" t="s">
         <v>18</v>
       </c>
       <c r="AE30" t="s">
-        <v>2125</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>2125</v>
-      </c>
-      <c r="AH30" t="n">
+        <v>2122</v>
+      </c>
+      <c r="AF30" t="n">
         <v>0</v>
       </c>
-      <c r="AI30" t="b">
+      <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="s">
-        <v>2176</v>
+      <c r="AH30" t="s">
+        <v>2173</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
       <c r="D31" t="s">
         <v>87</v>
@@ -10828,62 +10740,60 @@
         <v>377199</v>
       </c>
       <c r="U31" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="V31" t="n">
         <v>119825</v>
       </c>
       <c r="W31" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
       </c>
-      <c r="Y31"/>
-      <c r="Z31"/>
-      <c r="AA31" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="Y31" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z31" t="n">
         <v>0.100156383922298</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AA31" t="n">
         <v>0.0392957077622301</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>2143</v>
       </c>
       <c r="AD31" t="s">
         <v>18</v>
       </c>
       <c r="AE31" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AH31" t="n">
+        <v>2143</v>
+      </c>
+      <c r="AF31" t="n">
         <v>2</v>
       </c>
-      <c r="AI31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>2178</v>
+      <c r="AG31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>2175</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B32" t="s">
         <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
       <c r="D32" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="E32" t="n">
         <v>362321</v>
@@ -10934,59 +10844,57 @@
         <v>385519</v>
       </c>
       <c r="U32" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="V32" t="n">
         <v>228314</v>
       </c>
       <c r="W32" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
       </c>
-      <c r="Y32"/>
-      <c r="Z32"/>
-      <c r="AA32" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB32" t="n">
+      <c r="Y32" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.192908189546863</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AA32" t="n">
         <v>0.0637109664958376</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>2126</v>
       </c>
       <c r="AD32" t="s">
         <v>18</v>
       </c>
       <c r="AE32" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AH32" t="n">
+        <v>2126</v>
+      </c>
+      <c r="AF32" t="n">
         <v>0</v>
       </c>
-      <c r="AI32" t="b">
+      <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AJ32" t="s">
-        <v>2180</v>
+      <c r="AH32" t="s">
+        <v>2177</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B33" t="s">
         <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
       <c r="D33" t="s">
         <v>64</v>
@@ -11040,62 +10948,60 @@
         <v>371489</v>
       </c>
       <c r="U33" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
       <c r="V33" t="n">
         <v>515063</v>
       </c>
       <c r="W33" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X33" t="b">
         <v>1</v>
       </c>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="Y33" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z33" t="n">
         <v>0.135541503923493</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AA33" t="n">
         <v>0.0460412523788804</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>2180</v>
       </c>
       <c r="AD33" t="s">
         <v>18</v>
       </c>
       <c r="AE33" t="s">
-        <v>2183</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>2183</v>
-      </c>
-      <c r="AH33" t="n">
+        <v>2180</v>
+      </c>
+      <c r="AF33" t="n">
         <v>0</v>
       </c>
-      <c r="AI33" t="b">
+      <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="s">
-        <v>2184</v>
+      <c r="AH33" t="s">
+        <v>2181</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
       <c r="D34" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="E34" t="n">
         <v>357841</v>
@@ -11146,59 +11052,57 @@
         <v>385041</v>
       </c>
       <c r="U34" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="V34" t="n">
         <v>225338</v>
       </c>
       <c r="W34" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X34" t="b">
         <v>1</v>
       </c>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB34" t="n">
+      <c r="Y34" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z34" t="n">
         <v>0.0916182234884854</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AA34" t="n">
         <v>0.0300264800971488</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>2143</v>
       </c>
       <c r="AD34" t="s">
         <v>18</v>
       </c>
       <c r="AE34" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AH34" t="n">
+        <v>2143</v>
+      </c>
+      <c r="AF34" t="n">
         <v>0</v>
       </c>
-      <c r="AI34" t="b">
+      <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="s">
-        <v>2186</v>
+      <c r="AH34" t="s">
+        <v>2183</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B35" t="s">
         <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
       <c r="D35" t="s">
         <v>69</v>
@@ -11252,62 +11156,60 @@
         <v>375494</v>
       </c>
       <c r="U35" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="V35" t="n">
         <v>445258</v>
       </c>
       <c r="W35" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X35" t="b">
         <v>1</v>
       </c>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB35" t="n">
+      <c r="Y35" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z35" t="n">
         <v>0.0886859662597902</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AA35" t="n">
         <v>0.0310108381025968</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>2086</v>
       </c>
       <c r="AD35" t="s">
         <v>18</v>
       </c>
       <c r="AE35" t="s">
-        <v>2089</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>2089</v>
-      </c>
-      <c r="AH35" t="n">
+        <v>2086</v>
+      </c>
+      <c r="AF35" t="n">
         <v>0</v>
       </c>
-      <c r="AI35" t="b">
+      <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AJ35" t="s">
-        <v>2188</v>
+      <c r="AH35" t="s">
+        <v>2185</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B36" t="s">
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="D36" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="E36" t="n">
         <v>329109</v>
@@ -11358,62 +11260,60 @@
         <v>348923</v>
       </c>
       <c r="U36" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="V36" t="n">
         <v>684499</v>
       </c>
       <c r="W36" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X36" t="b">
         <v>1</v>
       </c>
-      <c r="Y36"/>
-      <c r="Z36"/>
-      <c r="AA36" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB36" t="n">
+      <c r="Y36" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z36" t="n">
         <v>-0.0612482585909469</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AA36" t="n">
         <v>0.0204764634070641</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>2126</v>
       </c>
       <c r="AD36" t="s">
         <v>18</v>
       </c>
       <c r="AE36" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AH36" t="n">
+        <v>2126</v>
+      </c>
+      <c r="AF36" t="n">
         <v>0</v>
       </c>
-      <c r="AI36" t="b">
+      <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AJ36" t="s">
-        <v>2191</v>
+      <c r="AH36" t="s">
+        <v>2188</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B37" t="s">
         <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>2192</v>
+        <v>2189</v>
       </c>
       <c r="D37" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="E37" t="n">
         <v>375494</v>
@@ -11464,62 +11364,60 @@
         <v>385519</v>
       </c>
       <c r="U37" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="V37" t="n">
         <v>720813</v>
       </c>
       <c r="W37" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X37" t="b">
         <v>1</v>
       </c>
-      <c r="Y37"/>
-      <c r="Z37"/>
-      <c r="AA37" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="Y37" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z37" t="n">
         <v>-0.0766491861186314</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AA37" t="n">
         <v>0.0270645794619827</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>2109</v>
       </c>
       <c r="AD37" t="s">
         <v>18</v>
       </c>
       <c r="AE37" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AF37" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AH37" t="n">
+        <v>2109</v>
+      </c>
+      <c r="AF37" t="n">
         <v>0</v>
       </c>
-      <c r="AI37" t="b">
+      <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AJ37" t="s">
-        <v>2192</v>
+      <c r="AH37" t="s">
+        <v>2189</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B38" t="s">
         <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>2193</v>
+        <v>2190</v>
       </c>
       <c r="D38" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
       <c r="E38" t="n">
         <v>357041</v>
@@ -11570,62 +11468,60 @@
         <v>372717</v>
       </c>
       <c r="U38" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="V38" t="n">
         <v>145160</v>
       </c>
       <c r="W38" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X38" t="b">
         <v>1</v>
       </c>
-      <c r="Y38"/>
-      <c r="Z38"/>
-      <c r="AA38" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="Y38" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z38" t="n">
         <v>-0.0971078291825149</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AA38" t="n">
         <v>0.0336344549088658</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>2159</v>
       </c>
       <c r="AD38" t="s">
         <v>18</v>
       </c>
       <c r="AE38" t="s">
-        <v>2162</v>
-      </c>
-      <c r="AF38" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>2162</v>
-      </c>
-      <c r="AH38" t="n">
+        <v>2159</v>
+      </c>
+      <c r="AF38" t="n">
         <v>0</v>
       </c>
-      <c r="AI38" t="b">
+      <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="s">
-        <v>2194</v>
+      <c r="AH38" t="s">
+        <v>2191</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B39" t="s">
         <v>15</v>
       </c>
       <c r="C39" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
       <c r="D39" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="E39" t="n">
         <v>357041</v>
@@ -11676,62 +11572,60 @@
         <v>385519</v>
       </c>
       <c r="U39" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="V39" t="n">
         <v>739951</v>
       </c>
       <c r="W39" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X39" t="b">
         <v>1</v>
       </c>
-      <c r="Y39"/>
-      <c r="Z39"/>
-      <c r="AA39" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="Y39" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z39" t="n">
         <v>0.378310974158291</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AA39" t="n">
         <v>0.13396783683577</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>2139</v>
       </c>
       <c r="AD39" t="s">
         <v>18</v>
       </c>
       <c r="AE39" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AF39" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AH39" t="n">
+        <v>2139</v>
+      </c>
+      <c r="AF39" t="n">
         <v>0</v>
       </c>
-      <c r="AI39" t="b">
+      <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="s">
-        <v>2196</v>
+      <c r="AH39" t="s">
+        <v>2193</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B40" t="s">
         <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
       <c r="D40" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="E40" t="n">
         <v>334704</v>
@@ -11782,62 +11676,60 @@
         <v>348923</v>
       </c>
       <c r="U40" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="V40" t="n">
         <v>254418</v>
       </c>
       <c r="W40" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X40" t="b">
         <v>1</v>
       </c>
-      <c r="Y40"/>
-      <c r="Z40"/>
-      <c r="AA40" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="Y40" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z40" t="n">
         <v>-0.0553183300808087</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AA40" t="n">
         <v>0.0204564104815819</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>2139</v>
       </c>
       <c r="AD40" t="s">
         <v>18</v>
       </c>
       <c r="AE40" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AF40" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG40" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AH40" t="n">
+        <v>2139</v>
+      </c>
+      <c r="AF40" t="n">
         <v>0</v>
       </c>
-      <c r="AI40" t="b">
+      <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="s">
-        <v>2197</v>
+      <c r="AH40" t="s">
+        <v>2194</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B41" t="s">
         <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="D41" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
       <c r="E41" t="n">
         <v>342051</v>
@@ -11888,59 +11780,57 @@
         <v>350521</v>
       </c>
       <c r="U41" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="V41" t="n">
         <v>350846</v>
       </c>
       <c r="W41" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X41" t="b">
         <v>1</v>
       </c>
-      <c r="Y41"/>
-      <c r="Z41"/>
-      <c r="AA41" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="Y41" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z41" t="n">
         <v>0.170350855318017</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AA41" t="n">
         <v>0.0580788061203405</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>2091</v>
       </c>
       <c r="AD41" t="s">
         <v>18</v>
       </c>
       <c r="AE41" t="s">
-        <v>2094</v>
-      </c>
-      <c r="AF41" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>2094</v>
-      </c>
-      <c r="AH41" t="n">
+        <v>2091</v>
+      </c>
+      <c r="AF41" t="n">
         <v>0</v>
       </c>
-      <c r="AI41" t="b">
+      <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AJ41" t="s">
-        <v>2200</v>
+      <c r="AH41" t="s">
+        <v>2197</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B42" t="s">
         <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>2201</v>
+        <v>2198</v>
       </c>
       <c r="D42" t="s">
         <v>57</v>
@@ -11994,62 +11884,60 @@
         <v>364650</v>
       </c>
       <c r="U42" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="V42" t="n">
         <v>381327</v>
       </c>
       <c r="W42" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X42" t="b">
         <v>1</v>
       </c>
-      <c r="Y42"/>
-      <c r="Z42"/>
-      <c r="AA42" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB42" t="n">
+      <c r="Y42" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z42" t="n">
         <v>-0.0201827049840121</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AA42" t="n">
         <v>0.0278414908062291</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>2159</v>
       </c>
       <c r="AD42" t="s">
         <v>18</v>
       </c>
       <c r="AE42" t="s">
-        <v>2162</v>
-      </c>
-      <c r="AF42" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG42" t="s">
-        <v>2162</v>
-      </c>
-      <c r="AH42" t="n">
+        <v>2159</v>
+      </c>
+      <c r="AF42" t="n">
         <v>3</v>
       </c>
-      <c r="AI42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>2202</v>
+      <c r="AG42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>2199</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B43" t="s">
         <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>2203</v>
+        <v>2200</v>
       </c>
       <c r="D43" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="E43" t="n">
         <v>348923</v>
@@ -12100,59 +11988,57 @@
         <v>357041</v>
       </c>
       <c r="U43" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="V43" t="n">
         <v>357453</v>
       </c>
       <c r="W43" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X43" t="b">
         <v>1</v>
       </c>
-      <c r="Y43"/>
-      <c r="Z43"/>
-      <c r="AA43" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB43" t="n">
+      <c r="Y43" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z43" t="n">
         <v>0.127521403045332</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AA43" t="n">
         <v>0.0520019698529636</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>2139</v>
       </c>
       <c r="AD43" t="s">
         <v>18</v>
       </c>
       <c r="AE43" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AF43" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG43" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AH43" t="n">
+        <v>2139</v>
+      </c>
+      <c r="AF43" t="n">
         <v>0</v>
       </c>
-      <c r="AI43" t="b">
+      <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AJ43" t="s">
-        <v>2204</v>
+      <c r="AH43" t="s">
+        <v>2201</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B44" t="s">
         <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="D44" t="s">
         <v>64</v>
@@ -12206,62 +12092,60 @@
         <v>371489</v>
       </c>
       <c r="U44" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
       <c r="V44" t="n">
         <v>260554</v>
       </c>
       <c r="W44" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X44" t="b">
         <v>1</v>
       </c>
-      <c r="Y44"/>
-      <c r="Z44"/>
-      <c r="AA44" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB44" t="n">
+      <c r="Y44" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z44" t="n">
         <v>0.210889511453941</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AA44" t="n">
         <v>0.0736144512488998</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>2100</v>
       </c>
       <c r="AD44" t="s">
         <v>18</v>
       </c>
       <c r="AE44" t="s">
-        <v>2103</v>
-      </c>
-      <c r="AF44" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG44" t="s">
-        <v>2103</v>
-      </c>
-      <c r="AH44" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AF44" t="n">
         <v>0</v>
       </c>
-      <c r="AI44" t="b">
+      <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AJ44" t="s">
-        <v>2205</v>
+      <c r="AH44" t="s">
+        <v>2202</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B45" t="s">
         <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>2206</v>
+        <v>2203</v>
       </c>
       <c r="D45" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="E45" t="n">
         <v>345331</v>
@@ -12312,59 +12196,57 @@
         <v>362321</v>
       </c>
       <c r="U45" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="V45" t="n">
         <v>27858</v>
       </c>
       <c r="W45" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X45" t="b">
         <v>1</v>
       </c>
-      <c r="Y45"/>
-      <c r="Z45"/>
-      <c r="AA45" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB45" t="n">
+      <c r="Y45" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z45" t="n">
         <v>0.104548341154732</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AA45" t="n">
         <v>0.0383712198329474</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>2143</v>
       </c>
       <c r="AD45" t="s">
         <v>18</v>
       </c>
       <c r="AE45" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AF45" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG45" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AH45" t="n">
+        <v>2143</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0</v>
       </c>
-      <c r="AI45" t="b">
+      <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="s">
-        <v>2207</v>
+      <c r="AH45" t="s">
+        <v>2204</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B46" t="s">
         <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>2208</v>
+        <v>2205</v>
       </c>
       <c r="D46" t="s">
         <v>57</v>
@@ -12418,62 +12300,60 @@
         <v>364650</v>
       </c>
       <c r="U46" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="V46" t="n">
         <v>8231</v>
       </c>
       <c r="W46" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X46" t="b">
         <v>1</v>
       </c>
-      <c r="Y46"/>
-      <c r="Z46"/>
-      <c r="AA46" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB46" t="n">
+      <c r="Y46" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z46" t="n">
         <v>-0.106853939541144</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AA46" t="n">
         <v>0.0381842114357521</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>2143</v>
       </c>
       <c r="AD46" t="s">
         <v>18</v>
       </c>
       <c r="AE46" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AF46" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG46" t="s">
-        <v>2146</v>
-      </c>
-      <c r="AH46" t="n">
+        <v>2143</v>
+      </c>
+      <c r="AF46" t="n">
         <v>0</v>
       </c>
-      <c r="AI46" t="b">
+      <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="s">
-        <v>2209</v>
+      <c r="AH46" t="s">
+        <v>2206</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B47" t="s">
         <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>2210</v>
+        <v>2207</v>
       </c>
       <c r="D47" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
       <c r="E47" t="n">
         <v>357041</v>
@@ -12524,62 +12404,60 @@
         <v>383573</v>
       </c>
       <c r="U47" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
       <c r="V47" t="n">
         <v>333727</v>
       </c>
       <c r="W47" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X47" t="b">
         <v>1</v>
       </c>
-      <c r="Y47"/>
-      <c r="Z47"/>
-      <c r="AA47" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB47" t="n">
+      <c r="Y47" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z47" t="n">
         <v>-0.260837707637534</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AA47" t="n">
         <v>0.0925970908294547</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>2105</v>
       </c>
       <c r="AD47" t="s">
         <v>18</v>
       </c>
       <c r="AE47" t="s">
-        <v>2108</v>
-      </c>
-      <c r="AF47" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG47" t="s">
-        <v>2108</v>
-      </c>
-      <c r="AH47" t="n">
+        <v>2105</v>
+      </c>
+      <c r="AF47" t="n">
         <v>0</v>
       </c>
-      <c r="AI47" t="b">
+      <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AJ47" t="s">
-        <v>2211</v>
+      <c r="AH47" t="s">
+        <v>2208</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B48" t="s">
         <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
       <c r="D48" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
       <c r="E48" t="n">
         <v>357041</v>
@@ -12630,59 +12508,57 @@
         <v>357841</v>
       </c>
       <c r="U48" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="V48" t="n">
         <v>26491</v>
       </c>
       <c r="W48" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X48" t="b">
         <v>1</v>
       </c>
-      <c r="Y48"/>
-      <c r="Z48"/>
-      <c r="AA48" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB48" t="n">
+      <c r="Y48" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z48" t="n">
         <v>-0.430420707372808</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AA48" t="n">
         <v>0.157044501592983</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>2126</v>
       </c>
       <c r="AD48" t="s">
         <v>18</v>
       </c>
       <c r="AE48" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AF48" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG48" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AH48" t="n">
+        <v>2126</v>
+      </c>
+      <c r="AF48" t="n">
         <v>0</v>
       </c>
-      <c r="AI48" t="b">
+      <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AJ48" t="s">
-        <v>2213</v>
+      <c r="AH48" t="s">
+        <v>2210</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B49" t="s">
         <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>2214</v>
+        <v>2211</v>
       </c>
       <c r="D49" t="s">
         <v>57</v>
@@ -12736,59 +12612,57 @@
         <v>364650</v>
       </c>
       <c r="U49" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="V49" t="n">
         <v>251751</v>
       </c>
       <c r="W49" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X49" t="b">
         <v>1</v>
       </c>
-      <c r="Y49"/>
-      <c r="Z49"/>
-      <c r="AA49" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB49" t="n">
+      <c r="Y49" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z49" t="n">
         <v>-0.0696494903297993</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AA49" t="n">
         <v>0.0259602396404736</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>2091</v>
       </c>
       <c r="AD49" t="s">
         <v>18</v>
       </c>
       <c r="AE49" t="s">
-        <v>2094</v>
-      </c>
-      <c r="AF49" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG49" t="s">
-        <v>2094</v>
-      </c>
-      <c r="AH49" t="n">
+        <v>2091</v>
+      </c>
+      <c r="AF49" t="n">
         <v>0</v>
       </c>
-      <c r="AI49" t="b">
+      <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AJ49" t="s">
-        <v>2215</v>
+      <c r="AH49" t="s">
+        <v>2212</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B50" t="s">
         <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>2216</v>
+        <v>2213</v>
       </c>
       <c r="D50" t="s">
         <v>58</v>
@@ -12842,62 +12716,60 @@
         <v>386608</v>
       </c>
       <c r="U50" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
       <c r="V50" t="n">
         <v>270247</v>
       </c>
       <c r="W50" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X50" t="b">
         <v>1</v>
       </c>
-      <c r="Y50"/>
-      <c r="Z50"/>
-      <c r="AA50" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB50" t="n">
+      <c r="Y50" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z50" t="n">
         <v>0.0789614474764663</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AA50" t="n">
         <v>0.0280513520180002</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>2122</v>
       </c>
       <c r="AD50" t="s">
         <v>18</v>
       </c>
       <c r="AE50" t="s">
-        <v>2125</v>
-      </c>
-      <c r="AF50" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG50" t="s">
-        <v>2125</v>
-      </c>
-      <c r="AH50" t="n">
+        <v>2122</v>
+      </c>
+      <c r="AF50" t="n">
         <v>0</v>
       </c>
-      <c r="AI50" t="b">
+      <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AJ50" t="s">
-        <v>2216</v>
+      <c r="AH50" t="s">
+        <v>2213</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B51" t="s">
         <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>2217</v>
+        <v>2214</v>
       </c>
       <c r="D51" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
       <c r="E51" t="n">
         <v>357041</v>
@@ -12948,62 +12820,60 @@
         <v>374227</v>
       </c>
       <c r="U51" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="V51" t="n">
         <v>1151621</v>
       </c>
       <c r="W51" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X51" t="b">
         <v>1</v>
       </c>
-      <c r="Y51"/>
-      <c r="Z51"/>
-      <c r="AA51" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB51" t="n">
+      <c r="Y51" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z51" t="n">
         <v>0.0940419049650525</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AA51" t="n">
         <v>0.0350749353985713</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>2109</v>
       </c>
       <c r="AD51" t="s">
         <v>18</v>
       </c>
       <c r="AE51" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AF51" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG51" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AH51" t="n">
+        <v>2109</v>
+      </c>
+      <c r="AF51" t="n">
         <v>0</v>
       </c>
-      <c r="AI51" t="b">
+      <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AJ51" t="s">
-        <v>2217</v>
+      <c r="AH51" t="s">
+        <v>2214</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B52" t="s">
         <v>15</v>
       </c>
       <c r="C52" t="s">
-        <v>2218</v>
+        <v>2215</v>
       </c>
       <c r="D52" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="E52" t="n">
         <v>348923</v>
@@ -13054,62 +12924,60 @@
         <v>362321</v>
       </c>
       <c r="U52" t="s">
-        <v>2219</v>
+        <v>2216</v>
       </c>
       <c r="V52" t="n">
         <v>75179</v>
       </c>
       <c r="W52" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X52" t="b">
         <v>1</v>
       </c>
-      <c r="Y52"/>
-      <c r="Z52"/>
-      <c r="AA52" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB52" t="n">
+      <c r="Y52" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z52" t="n">
         <v>-0.0347899841166762</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AA52" t="n">
         <v>0.0144652723765375</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>2217</v>
       </c>
       <c r="AD52" t="s">
         <v>18</v>
       </c>
       <c r="AE52" t="s">
-        <v>2220</v>
-      </c>
-      <c r="AF52" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG52" t="s">
-        <v>2220</v>
-      </c>
-      <c r="AH52" t="n">
+        <v>2217</v>
+      </c>
+      <c r="AF52" t="n">
         <v>0</v>
       </c>
-      <c r="AI52" t="b">
+      <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AJ52" t="s">
-        <v>2221</v>
+      <c r="AH52" t="s">
+        <v>2218</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B53" t="s">
         <v>15</v>
       </c>
       <c r="C53" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="D53" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="E53" t="n">
         <v>371489</v>
@@ -13160,62 +13028,60 @@
         <v>385041</v>
       </c>
       <c r="U53" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="V53" t="n">
         <v>327744</v>
       </c>
       <c r="W53" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X53" t="b">
         <v>1</v>
       </c>
-      <c r="Y53"/>
-      <c r="Z53"/>
-      <c r="AA53" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB53" t="n">
+      <c r="Y53" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z53" t="n">
         <v>0.110453843288698</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AA53" t="n">
         <v>0.0417848328136782</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>2126</v>
       </c>
       <c r="AD53" t="s">
         <v>18</v>
       </c>
       <c r="AE53" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AF53" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG53" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AH53" t="n">
+        <v>2126</v>
+      </c>
+      <c r="AF53" t="n">
         <v>0</v>
       </c>
-      <c r="AI53" t="b">
+      <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AJ53" t="s">
-        <v>2223</v>
+      <c r="AH53" t="s">
+        <v>2220</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B54" t="s">
         <v>15</v>
       </c>
       <c r="C54" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="D54" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="E54" t="n">
         <v>348923</v>
@@ -13266,62 +13132,60 @@
         <v>385041</v>
       </c>
       <c r="U54" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
       <c r="V54" t="n">
         <v>582283</v>
       </c>
       <c r="W54" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X54" t="b">
         <v>1</v>
       </c>
-      <c r="Y54"/>
-      <c r="Z54"/>
-      <c r="AA54" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB54" t="n">
+      <c r="Y54" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z54" t="n">
         <v>0.126021935080029</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AA54" t="n">
         <v>0.0587235864325284</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>2180</v>
       </c>
       <c r="AD54" t="s">
         <v>18</v>
       </c>
       <c r="AE54" t="s">
-        <v>2183</v>
-      </c>
-      <c r="AF54" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG54" t="s">
-        <v>2183</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ54" t="s">
-        <v>2225</v>
+        <v>2180</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH54" t="s">
+        <v>2222</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B55" t="s">
         <v>15</v>
       </c>
       <c r="C55" t="s">
-        <v>2226</v>
+        <v>2223</v>
       </c>
       <c r="D55" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="E55" t="n">
         <v>345331</v>
@@ -13372,59 +13236,57 @@
         <v>362321</v>
       </c>
       <c r="U55" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="V55" t="n">
         <v>371685</v>
       </c>
       <c r="W55" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X55" t="b">
         <v>1</v>
       </c>
-      <c r="Y55"/>
-      <c r="Z55"/>
-      <c r="AA55" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB55" t="n">
+      <c r="Y55" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z55" t="n">
         <v>0.0856308508717971</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AA55" t="n">
         <v>0.0353679473671562</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>2114</v>
       </c>
       <c r="AD55" t="s">
         <v>18</v>
       </c>
       <c r="AE55" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AF55" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG55" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AH55" t="n">
+        <v>2114</v>
+      </c>
+      <c r="AF55" t="n">
         <v>0</v>
       </c>
-      <c r="AI55" t="b">
+      <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AJ55" t="s">
-        <v>2226</v>
+      <c r="AH55" t="s">
+        <v>2223</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B56" t="s">
         <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>2227</v>
+        <v>2224</v>
       </c>
       <c r="D56" t="s">
         <v>58</v>
@@ -13478,62 +13340,60 @@
         <v>386608</v>
       </c>
       <c r="U56" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="V56" t="n">
         <v>133437</v>
       </c>
       <c r="W56" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X56" t="b">
         <v>1</v>
       </c>
-      <c r="Y56"/>
-      <c r="Z56"/>
-      <c r="AA56" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB56" t="n">
+      <c r="Y56" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z56" t="n">
         <v>-0.0535179459242971</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AA56" t="n">
         <v>0.026110430111561</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>2109</v>
       </c>
       <c r="AD56" t="s">
         <v>18</v>
       </c>
       <c r="AE56" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AF56" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG56" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ56" t="s">
-        <v>2228</v>
+        <v>2109</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>2225</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B57" t="s">
         <v>15</v>
       </c>
       <c r="C57" t="s">
-        <v>2229</v>
+        <v>2226</v>
       </c>
       <c r="D57" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="E57" t="n">
         <v>383573</v>
@@ -13584,62 +13444,60 @@
         <v>392315</v>
       </c>
       <c r="U57" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="V57" t="n">
         <v>906116</v>
       </c>
       <c r="W57" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X57" t="b">
         <v>1</v>
       </c>
-      <c r="Y57"/>
-      <c r="Z57"/>
-      <c r="AA57" t="s">
-        <v>2138</v>
-      </c>
-      <c r="AB57" t="n">
+      <c r="Y57" t="s">
+        <v>2135</v>
+      </c>
+      <c r="Z57" t="n">
         <v>-0.0745278327413063</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AA57" t="n">
         <v>0.0289285000623679</v>
+      </c>
+      <c r="AB57" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC57" t="s">
+        <v>2114</v>
       </c>
       <c r="AD57" t="s">
         <v>18</v>
       </c>
       <c r="AE57" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AF57" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG57" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AH57" t="n">
+        <v>2114</v>
+      </c>
+      <c r="AF57" t="n">
         <v>0</v>
       </c>
-      <c r="AI57" t="b">
+      <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="s">
-        <v>2230</v>
+      <c r="AH57" t="s">
+        <v>2227</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B58" t="s">
         <v>15</v>
       </c>
       <c r="C58" t="s">
-        <v>2231</v>
+        <v>2228</v>
       </c>
       <c r="D58" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="E58" t="n">
         <v>357041</v>
@@ -13690,59 +13548,57 @@
         <v>385041</v>
       </c>
       <c r="U58" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="V58" t="n">
         <v>830935</v>
       </c>
       <c r="W58" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X58" t="b">
         <v>1</v>
       </c>
-      <c r="Y58"/>
-      <c r="Z58"/>
-      <c r="AA58" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB58" t="n">
+      <c r="Y58" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z58" t="n">
         <v>0.310647881114924</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AA58" t="n">
         <v>0.119407609531995</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>2126</v>
       </c>
       <c r="AD58" t="s">
         <v>18</v>
       </c>
       <c r="AE58" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AF58" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG58" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AH58" t="n">
+        <v>2126</v>
+      </c>
+      <c r="AF58" t="n">
         <v>0</v>
       </c>
-      <c r="AI58" t="b">
+      <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AJ58" t="s">
-        <v>2232</v>
+      <c r="AH58" t="s">
+        <v>2229</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B59" t="s">
         <v>15</v>
       </c>
       <c r="C59" t="s">
-        <v>2233</v>
+        <v>2230</v>
       </c>
       <c r="D59" t="s">
         <v>87</v>
@@ -13796,62 +13652,60 @@
         <v>377199</v>
       </c>
       <c r="U59" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="V59" t="n">
         <v>932967</v>
       </c>
       <c r="W59" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X59" t="b">
         <v>1</v>
       </c>
-      <c r="Y59"/>
-      <c r="Z59"/>
-      <c r="AA59" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB59" t="n">
+      <c r="Y59" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z59" t="n">
         <v>0.101371200137544</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AA59" t="n">
         <v>0.0610658578223545</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>2086</v>
       </c>
       <c r="AD59" t="s">
         <v>18</v>
       </c>
       <c r="AE59" t="s">
-        <v>2089</v>
-      </c>
-      <c r="AF59" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG59" t="s">
-        <v>2089</v>
-      </c>
-      <c r="AH59" t="n">
+        <v>2086</v>
+      </c>
+      <c r="AF59" t="n">
         <v>2</v>
       </c>
-      <c r="AI59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ59" t="s">
-        <v>2233</v>
+      <c r="AG59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH59" t="s">
+        <v>2230</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B60" t="s">
         <v>15</v>
       </c>
       <c r="C60" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="D60" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="E60" t="n">
         <v>377199</v>
@@ -13902,62 +13756,60 @@
         <v>385519</v>
       </c>
       <c r="U60" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="V60" t="n">
         <v>498096</v>
       </c>
       <c r="W60" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X60" t="b">
         <v>1</v>
       </c>
-      <c r="Y60"/>
-      <c r="Z60"/>
-      <c r="AA60" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB60" t="n">
+      <c r="Y60" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z60" t="n">
         <v>0.0606802605227468</v>
       </c>
-      <c r="AC60" t="n">
+      <c r="AA60" t="n">
         <v>0.0247930486525363</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC60" t="s">
+        <v>2126</v>
       </c>
       <c r="AD60" t="s">
         <v>18</v>
       </c>
       <c r="AE60" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AF60" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG60" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AH60" t="n">
+        <v>2126</v>
+      </c>
+      <c r="AF60" t="n">
         <v>0</v>
       </c>
-      <c r="AI60" t="b">
+      <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="s">
-        <v>2235</v>
+      <c r="AH60" t="s">
+        <v>2232</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B61" t="s">
         <v>15</v>
       </c>
       <c r="C61" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="D61" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
       <c r="E61" t="n">
         <v>344309</v>
@@ -14008,62 +13860,60 @@
         <v>357841</v>
       </c>
       <c r="U61" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="V61" t="n">
         <v>538577</v>
       </c>
       <c r="W61" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X61" t="b">
         <v>1</v>
       </c>
-      <c r="Y61"/>
-      <c r="Z61"/>
-      <c r="AA61" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB61" t="n">
+      <c r="Y61" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z61" t="n">
         <v>-0.0480892381343059</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AA61" t="n">
         <v>0.0208137412067843</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>2086</v>
       </c>
       <c r="AD61" t="s">
         <v>18</v>
       </c>
       <c r="AE61" t="s">
-        <v>2089</v>
-      </c>
-      <c r="AF61" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG61" t="s">
-        <v>2089</v>
-      </c>
-      <c r="AH61" t="n">
+        <v>2086</v>
+      </c>
+      <c r="AF61" t="n">
         <v>0</v>
       </c>
-      <c r="AI61" t="b">
+      <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AJ61" t="s">
-        <v>2237</v>
+      <c r="AH61" t="s">
+        <v>2234</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B62" t="s">
         <v>15</v>
       </c>
       <c r="C62" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="D62" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="E62" t="n">
         <v>350521</v>
@@ -14114,62 +13964,60 @@
         <v>385041</v>
       </c>
       <c r="U62" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="V62" t="n">
         <v>664270</v>
       </c>
       <c r="W62" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X62" t="b">
         <v>1</v>
       </c>
-      <c r="Y62"/>
-      <c r="Z62"/>
-      <c r="AA62" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB62" t="n">
+      <c r="Y62" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z62" t="n">
         <v>0.0895288563032054</v>
       </c>
-      <c r="AC62" t="n">
+      <c r="AA62" t="n">
         <v>0.0355728914315874</v>
+      </c>
+      <c r="AB62" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>2139</v>
       </c>
       <c r="AD62" t="s">
         <v>18</v>
       </c>
       <c r="AE62" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AF62" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG62" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AH62" t="n">
+        <v>2139</v>
+      </c>
+      <c r="AF62" t="n">
         <v>0</v>
       </c>
-      <c r="AI62" t="b">
+      <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AJ62" t="s">
-        <v>2239</v>
+      <c r="AH62" t="s">
+        <v>2236</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B63" t="s">
         <v>15</v>
       </c>
       <c r="C63" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
       <c r="D63" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
       <c r="E63" t="n">
         <v>334704</v>
@@ -14220,62 +14068,60 @@
         <v>357841</v>
       </c>
       <c r="U63" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="V63" t="n">
         <v>838969</v>
       </c>
       <c r="W63" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X63" t="b">
         <v>1</v>
       </c>
-      <c r="Y63"/>
-      <c r="Z63"/>
-      <c r="AA63" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB63" t="n">
+      <c r="Y63" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z63" t="n">
         <v>-0.182461076293907</v>
       </c>
-      <c r="AC63" t="n">
+      <c r="AA63" t="n">
         <v>0.0750583063606093</v>
+      </c>
+      <c r="AB63" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC63" t="s">
+        <v>2114</v>
       </c>
       <c r="AD63" t="s">
         <v>18</v>
       </c>
       <c r="AE63" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AF63" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG63" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AH63" t="n">
+        <v>2114</v>
+      </c>
+      <c r="AF63" t="n">
         <v>0</v>
       </c>
-      <c r="AI63" t="b">
+      <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="s">
-        <v>2241</v>
+      <c r="AH63" t="s">
+        <v>2238</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B64" t="s">
         <v>15</v>
       </c>
       <c r="C64" t="s">
-        <v>2242</v>
+        <v>2239</v>
       </c>
       <c r="D64" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
       <c r="E64" t="n">
         <v>371489</v>
@@ -14326,59 +14172,57 @@
         <v>383573</v>
       </c>
       <c r="U64" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="V64" t="n">
         <v>133043</v>
       </c>
       <c r="W64" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X64" t="b">
         <v>1</v>
       </c>
-      <c r="Y64"/>
-      <c r="Z64"/>
-      <c r="AA64" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB64" t="n">
+      <c r="Y64" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z64" t="n">
         <v>-0.132847281520434</v>
       </c>
-      <c r="AC64" t="n">
+      <c r="AA64" t="n">
         <v>0.0539828816651416</v>
+      </c>
+      <c r="AB64" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>2126</v>
       </c>
       <c r="AD64" t="s">
         <v>18</v>
       </c>
       <c r="AE64" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AF64" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG64" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AH64" t="n">
+        <v>2126</v>
+      </c>
+      <c r="AF64" t="n">
         <v>0</v>
       </c>
-      <c r="AI64" t="b">
+      <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AJ64" t="s">
-        <v>2243</v>
+      <c r="AH64" t="s">
+        <v>2240</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B65" t="s">
         <v>15</v>
       </c>
       <c r="C65" t="s">
-        <v>2244</v>
+        <v>2241</v>
       </c>
       <c r="D65" t="s">
         <v>57</v>
@@ -14432,62 +14276,60 @@
         <v>364650</v>
       </c>
       <c r="U65" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
       <c r="V65" t="n">
         <v>539308</v>
       </c>
       <c r="W65" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X65" t="b">
         <v>1</v>
       </c>
-      <c r="Y65"/>
-      <c r="Z65"/>
-      <c r="AA65" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB65" t="n">
+      <c r="Y65" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z65" t="n">
         <v>-0.0799811786668031</v>
       </c>
-      <c r="AC65" t="n">
+      <c r="AA65" t="n">
         <v>0.0399083777030844</v>
+      </c>
+      <c r="AB65" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>2100</v>
       </c>
       <c r="AD65" t="s">
         <v>18</v>
       </c>
       <c r="AE65" t="s">
-        <v>2103</v>
-      </c>
-      <c r="AF65" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG65" t="s">
-        <v>2103</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ65" t="s">
-        <v>2245</v>
+        <v>2100</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH65" t="s">
+        <v>2242</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B66" t="s">
         <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D66" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
       <c r="E66" t="n">
         <v>348923</v>
@@ -14538,59 +14380,57 @@
         <v>357841</v>
       </c>
       <c r="U66" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="V66" t="n">
         <v>1344397</v>
       </c>
       <c r="W66" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X66" t="b">
         <v>1</v>
       </c>
-      <c r="Y66"/>
-      <c r="Z66"/>
-      <c r="AA66" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB66" t="n">
+      <c r="Y66" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z66" t="n">
         <v>-0.123603132852417</v>
       </c>
-      <c r="AC66" t="n">
+      <c r="AA66" t="n">
         <v>0.057017107271425</v>
+      </c>
+      <c r="AB66" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>2109</v>
       </c>
       <c r="AD66" t="s">
         <v>18</v>
       </c>
       <c r="AE66" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AF66" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG66" t="s">
-        <v>2112</v>
-      </c>
-      <c r="AH66" t="n">
+        <v>2109</v>
+      </c>
+      <c r="AF66" t="n">
         <v>0</v>
       </c>
-      <c r="AI66" t="b">
+      <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AJ66" t="s">
-        <v>2247</v>
+      <c r="AH66" t="s">
+        <v>2244</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B67" t="s">
         <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>2248</v>
+        <v>2245</v>
       </c>
       <c r="D67" t="s">
         <v>14</v>
@@ -14644,62 +14484,60 @@
         <v>378078</v>
       </c>
       <c r="U67" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="V67" t="n">
         <v>677165</v>
       </c>
       <c r="W67" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X67" t="b">
         <v>1</v>
       </c>
-      <c r="Y67"/>
-      <c r="Z67"/>
-      <c r="AA67" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB67" t="n">
+      <c r="Y67" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z67" t="n">
         <v>0.0543227080388035</v>
       </c>
-      <c r="AC67" t="n">
+      <c r="AA67" t="n">
         <v>0.0287947592185852</v>
+      </c>
+      <c r="AB67" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC67" t="s">
+        <v>2126</v>
       </c>
       <c r="AD67" t="s">
         <v>18</v>
       </c>
       <c r="AE67" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AF67" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG67" t="s">
-        <v>2129</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI67" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ67" t="s">
-        <v>2249</v>
+        <v>2126</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>2246</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B68" t="s">
         <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
       <c r="D68" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="E68" t="n">
         <v>348923</v>
@@ -14750,62 +14588,60 @@
         <v>362321</v>
       </c>
       <c r="U68" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
       <c r="V68" t="n">
         <v>532194</v>
       </c>
       <c r="W68" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X68" t="b">
         <v>1</v>
       </c>
-      <c r="Y68"/>
-      <c r="Z68"/>
-      <c r="AA68" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB68" t="n">
+      <c r="Y68" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z68" t="n">
         <v>0.0859446785153919</v>
       </c>
-      <c r="AC68" t="n">
+      <c r="AA68" t="n">
         <v>0.0399493971667464</v>
+      </c>
+      <c r="AB68" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC68" t="s">
+        <v>2180</v>
       </c>
       <c r="AD68" t="s">
         <v>18</v>
       </c>
       <c r="AE68" t="s">
-        <v>2183</v>
-      </c>
-      <c r="AF68" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG68" t="s">
-        <v>2183</v>
-      </c>
-      <c r="AH68" t="n">
+        <v>2180</v>
+      </c>
+      <c r="AF68" t="n">
         <v>0</v>
       </c>
-      <c r="AI68" t="b">
+      <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AJ68" t="s">
-        <v>2251</v>
+      <c r="AH68" t="s">
+        <v>2248</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B69" t="s">
         <v>15</v>
       </c>
       <c r="C69" t="s">
-        <v>2252</v>
+        <v>2249</v>
       </c>
       <c r="D69" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="E69" t="n">
         <v>342051</v>
@@ -14856,59 +14692,57 @@
         <v>385041</v>
       </c>
       <c r="U69" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="V69" t="n">
         <v>623581</v>
       </c>
       <c r="W69" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X69" t="b">
         <v>1</v>
       </c>
-      <c r="Y69"/>
-      <c r="Z69"/>
-      <c r="AA69" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB69" t="n">
+      <c r="Y69" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z69" t="n">
         <v>0.0423564762232915</v>
       </c>
-      <c r="AC69" t="n">
+      <c r="AA69" t="n">
         <v>0.0181817632872472</v>
+      </c>
+      <c r="AB69" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC69" t="s">
+        <v>2159</v>
       </c>
       <c r="AD69" t="s">
         <v>18</v>
       </c>
       <c r="AE69" t="s">
-        <v>2162</v>
-      </c>
-      <c r="AF69" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG69" t="s">
-        <v>2162</v>
-      </c>
-      <c r="AH69" t="n">
+        <v>2159</v>
+      </c>
+      <c r="AF69" t="n">
         <v>0</v>
       </c>
-      <c r="AI69" t="b">
+      <c r="AG69" t="b">
         <v>0</v>
       </c>
-      <c r="AJ69" t="s">
-        <v>2253</v>
+      <c r="AH69" t="s">
+        <v>2250</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="B70" t="s">
         <v>15</v>
       </c>
       <c r="C70" t="s">
-        <v>2254</v>
+        <v>2251</v>
       </c>
       <c r="D70" t="s">
         <v>57</v>
@@ -14962,48 +14796,46 @@
         <v>364650</v>
       </c>
       <c r="U70" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
       <c r="V70" t="n">
         <v>789235</v>
       </c>
       <c r="W70" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="X70" t="b">
         <v>1</v>
       </c>
-      <c r="Y70"/>
-      <c r="Z70"/>
-      <c r="AA70" t="s">
-        <v>2088</v>
-      </c>
-      <c r="AB70" t="n">
+      <c r="Y70" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z70" t="n">
         <v>-0.070708804111022</v>
       </c>
-      <c r="AC70" t="n">
+      <c r="AA70" t="n">
         <v>0.0346457147201427</v>
+      </c>
+      <c r="AB70" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC70" t="s">
+        <v>2122</v>
       </c>
       <c r="AD70" t="s">
         <v>18</v>
       </c>
       <c r="AE70" t="s">
-        <v>2125</v>
-      </c>
-      <c r="AF70" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG70" t="s">
-        <v>2125</v>
-      </c>
-      <c r="AH70" t="n">
+        <v>2122</v>
+      </c>
+      <c r="AF70" t="n">
         <v>0</v>
       </c>
-      <c r="AI70" t="b">
+      <c r="AG70" t="b">
         <v>0</v>
       </c>
-      <c r="AJ70" t="s">
-        <v>2255</v>
+      <c r="AH70" t="s">
+        <v>2252</v>
       </c>
     </row>
   </sheetData>
@@ -15082,37 +14914,28 @@
         <v>2070</v>
       </c>
       <c r="V1" t="s">
-        <v>2256</v>
+        <v>40</v>
       </c>
       <c r="W1" t="s">
-        <v>2257</v>
+        <v>2074</v>
       </c>
       <c r="X1" t="s">
-        <v>2258</v>
+        <v>2075</v>
       </c>
       <c r="Y1" t="s">
-        <v>2259</v>
+        <v>2076</v>
       </c>
       <c r="Z1" t="s">
-        <v>2260</v>
+        <v>12</v>
       </c>
       <c r="AA1" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AB1" t="s">
-        <v>2079</v>
+        <v>2253</v>
       </c>
       <c r="AC1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" t="s">
         <v>2080</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>2261</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>2083</v>
       </c>
     </row>
     <row r="2">
@@ -15120,10 +14943,10 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>2262</v>
+        <v>2254</v>
       </c>
       <c r="C2" t="s">
-        <v>2263</v>
+        <v>2255</v>
       </c>
       <c r="D2" t="n">
         <v>392315</v>
@@ -15180,37 +15003,28 @@
         <v>394846</v>
       </c>
       <c r="V2" t="n">
-        <v>-4.65691787937549</v>
+        <v>-0.511923290338465</v>
       </c>
       <c r="W2" t="n">
-        <v>-4.25512254643836</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-2.92765615320275</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-3.27777448812311</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-4.86512579862786</v>
+        <v>0.126096441187357</v>
+      </c>
+      <c r="X2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>18</v>
       </c>
       <c r="AA2" t="s">
         <v>18</v>
       </c>
-      <c r="AB2" t="s">
-        <v>18</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>2264</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="3">
@@ -15218,10 +15032,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>2265</v>
+        <v>2257</v>
       </c>
       <c r="C3" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="D3" t="n">
         <v>111703</v>
@@ -15278,37 +15092,28 @@
         <v>355827</v>
       </c>
       <c r="V3" t="n">
-        <v>-3.69246672525229</v>
+        <v>-0.100615047828368</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0200401215527074</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-2.44934318406055</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-0.471609222185606</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-1.05438102534704</v>
+        <v>0.0628299951076476</v>
+      </c>
+      <c r="X3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>18</v>
       </c>
       <c r="AA3" t="s">
         <v>18</v>
       </c>
-      <c r="AB3" t="s">
-        <v>18</v>
+      <c r="AB3" t="n">
+        <v>0.00422997912124142</v>
       </c>
       <c r="AC3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.00422997912124142</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>2265</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="4">
@@ -15316,10 +15121,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>2266</v>
+        <v>2258</v>
       </c>
       <c r="C4" t="s">
-        <v>2267</v>
+        <v>2259</v>
       </c>
       <c r="D4" t="n">
         <v>44796</v>
@@ -15376,37 +15181,28 @@
         <v>392223</v>
       </c>
       <c r="V4" t="n">
-        <v>1.79506931546413</v>
+        <v>0.0493722647574671</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.89430146403801</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.46419682701213</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.928457210993792</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-1.0726201354991</v>
+        <v>0.125682973109206</v>
+      </c>
+      <c r="X4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>18</v>
       </c>
       <c r="AA4" t="s">
         <v>18</v>
       </c>
-      <c r="AB4" t="s">
-        <v>18</v>
+      <c r="AB4" t="n">
+        <v>0.00432878339237942</v>
       </c>
       <c r="AC4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.00432878339237942</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>2268</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="5">
@@ -15414,10 +15210,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>2269</v>
+        <v>2261</v>
       </c>
       <c r="C5" t="s">
-        <v>2270</v>
+        <v>2262</v>
       </c>
       <c r="D5" t="n">
         <v>935861</v>
@@ -15474,37 +15270,28 @@
         <v>360084</v>
       </c>
       <c r="V5" t="n">
-        <v>2.76628342263009</v>
+        <v>0.0418349434617707</v>
       </c>
       <c r="W5" t="n">
-        <v>0.508452449223444</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.54711006281813</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-2.41818306713396</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.739495413126521</v>
+        <v>0.0574328829408099</v>
+      </c>
+      <c r="X5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>18</v>
       </c>
       <c r="AA5" t="s">
         <v>18</v>
       </c>
-      <c r="AB5" t="s">
-        <v>18</v>
+      <c r="AB5" t="n">
+        <v>0.00475524475524476</v>
       </c>
       <c r="AC5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.00475524475524476</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>2271</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="6">
@@ -15512,10 +15299,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>2272</v>
+        <v>2264</v>
       </c>
       <c r="C6" t="s">
-        <v>2273</v>
+        <v>2265</v>
       </c>
       <c r="D6" t="n">
         <v>180027</v>
@@ -15572,37 +15359,28 @@
         <v>379726</v>
       </c>
       <c r="V6" t="n">
-        <v>3.58114027044037</v>
+        <v>0.088375314668952</v>
       </c>
       <c r="W6" t="n">
-        <v>1.43916384818508</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.863204323370988</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.47695328201824</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-0.332912130971472</v>
+        <v>0.0751327109495719</v>
+      </c>
+      <c r="X6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>18</v>
       </c>
       <c r="AA6" t="s">
         <v>18</v>
       </c>
-      <c r="AB6" t="s">
-        <v>18</v>
+      <c r="AB6" t="n">
+        <v>0.0132910828357627</v>
       </c>
       <c r="AC6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.0132910828357627</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>2274</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="7">
@@ -15610,10 +15388,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>2275</v>
+        <v>2267</v>
       </c>
       <c r="C7" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="D7" t="n">
         <v>312897</v>
@@ -15670,37 +15448,28 @@
         <v>358636</v>
       </c>
       <c r="V7" t="n">
-        <v>2.92078991557302</v>
+        <v>0.0373909553411684</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22856588813814</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.46264113468706</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-2.15790013810069</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-0.987635452054143</v>
+        <v>0.0504577954857272</v>
+      </c>
+      <c r="X7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>18</v>
       </c>
       <c r="AA7" t="s">
         <v>18</v>
       </c>
-      <c r="AB7" t="s">
-        <v>18</v>
+      <c r="AB7" t="n">
+        <v>0.0149011031843679</v>
       </c>
       <c r="AC7" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.0149011031843679</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>2276</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="8">
@@ -15708,10 +15477,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>2277</v>
+        <v>2269</v>
       </c>
       <c r="C8" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="D8" t="n">
         <v>290162</v>
@@ -15768,37 +15537,28 @@
         <v>362105</v>
       </c>
       <c r="V8" t="n">
-        <v>0.414873872515072</v>
+        <v>0.0557426627228523</v>
       </c>
       <c r="W8" t="n">
-        <v>1.29869614502596</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.195770540030452</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>3.40014586708147</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.51174320300081</v>
+        <v>0.0444166896153551</v>
+      </c>
+      <c r="X8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>18</v>
       </c>
       <c r="AA8" t="s">
         <v>18</v>
       </c>
-      <c r="AB8" t="s">
-        <v>18</v>
+      <c r="AB8" t="n">
+        <v>0.0305494330411319</v>
       </c>
       <c r="AC8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.0305494330411319</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>2278</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="9">
@@ -15806,10 +15566,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>2279</v>
+        <v>2271</v>
       </c>
       <c r="C9" t="s">
-        <v>2280</v>
+        <v>2272</v>
       </c>
       <c r="D9" t="n">
         <v>2283</v>
@@ -15866,37 +15626,28 @@
         <v>350512</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53178196003094</v>
+        <v>-0.00860130576532818</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.393751570529677</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-3.22418391839075</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.56079222499625</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-0.304045138552332</v>
+        <v>0.0980117547185968</v>
+      </c>
+      <c r="X9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>18</v>
       </c>
       <c r="AA9" t="s">
         <v>18</v>
       </c>
-      <c r="AB9" t="s">
-        <v>18</v>
+      <c r="AB9" t="n">
+        <v>0.0338057107131259</v>
       </c>
       <c r="AC9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.0338057107131259</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>2281</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="10">
@@ -15904,10 +15655,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>2282</v>
+        <v>2274</v>
       </c>
       <c r="C10" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
       <c r="D10" t="n">
         <v>2283</v>
@@ -15964,37 +15715,28 @@
         <v>353058</v>
       </c>
       <c r="V10" t="n">
-        <v>1.87283230592382</v>
+        <v>-0.0671402195746843</v>
       </c>
       <c r="W10" t="n">
-        <v>0.328064004731053</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-1.56194328315892</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-1.02020297527346</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-2.87413631288292</v>
+        <v>0.13542603747696</v>
+      </c>
+      <c r="X10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>18</v>
       </c>
       <c r="AA10" t="s">
         <v>18</v>
       </c>
-      <c r="AB10" t="s">
-        <v>18</v>
+      <c r="AB10" t="n">
+        <v>0.0353408151529748</v>
       </c>
       <c r="AC10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.0353408151529748</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>2283</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="11">
@@ -16002,10 +15744,10 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>2284</v>
+        <v>2276</v>
       </c>
       <c r="C11" t="s">
-        <v>2285</v>
+        <v>2277</v>
       </c>
       <c r="D11" t="n">
         <v>260913</v>
@@ -16062,37 +15804,28 @@
         <v>377609</v>
       </c>
       <c r="V11" t="n">
-        <v>1.11890017713395</v>
+        <v>0.148643471777773</v>
       </c>
       <c r="W11" t="n">
-        <v>0.866206067330214</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.08010530301502</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>3.44585496263805</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-0.206060052778658</v>
+        <v>0.123696172652451</v>
+      </c>
+      <c r="X11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>18</v>
       </c>
       <c r="AA11" t="s">
         <v>18</v>
       </c>
-      <c r="AB11" t="s">
-        <v>18</v>
+      <c r="AB11" t="n">
+        <v>0.0401563764619557</v>
       </c>
       <c r="AC11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.0401563764619557</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>2286</v>
+        <v>2278</v>
       </c>
     </row>
   </sheetData>
@@ -16123,34 +15856,34 @@
         <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>2287</v>
+        <v>2279</v>
       </c>
       <c r="G1" t="s">
         <v>576</v>
       </c>
       <c r="H1" t="s">
-        <v>2288</v>
+        <v>2280</v>
       </c>
       <c r="I1" t="s">
-        <v>2289</v>
+        <v>2281</v>
       </c>
       <c r="J1" t="s">
         <v>587</v>
       </c>
       <c r="K1" t="s">
-        <v>2290</v>
+        <v>2282</v>
       </c>
       <c r="L1" t="s">
-        <v>2291</v>
+        <v>2283</v>
       </c>
       <c r="M1" t="s">
-        <v>2292</v>
+        <v>2284</v>
       </c>
       <c r="N1" t="s">
-        <v>2293</v>
+        <v>2285</v>
       </c>
       <c r="O1" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="P1" t="s">
         <v>2070</v>
@@ -16170,33 +15903,33 @@
         <v>1266</v>
       </c>
       <c r="E2" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F2" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G2" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>2297</v>
+        <v>2289</v>
       </c>
       <c r="K2" t="s">
-        <v>2298</v>
+        <v>2290</v>
       </c>
       <c r="L2" t="s">
-        <v>2297</v>
+        <v>2289</v>
       </c>
       <c r="M2" t="s">
-        <v>2299</v>
+        <v>2291</v>
       </c>
       <c r="N2" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O2" t="s">
-        <v>2301</v>
+        <v>2293</v>
       </c>
       <c r="P2" t="n">
         <v>343952</v>
@@ -16216,33 +15949,33 @@
         <v>363</v>
       </c>
       <c r="E3" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F3" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G3" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>2303</v>
+        <v>2295</v>
       </c>
       <c r="K3" t="s">
-        <v>2304</v>
+        <v>2296</v>
       </c>
       <c r="L3" t="s">
-        <v>2303</v>
+        <v>2295</v>
       </c>
       <c r="M3" t="s">
-        <v>2305</v>
+        <v>2297</v>
       </c>
       <c r="N3" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O3" t="s">
-        <v>2306</v>
+        <v>2298</v>
       </c>
       <c r="P3" t="n">
         <v>344972</v>
@@ -16262,30 +15995,30 @@
         <v>366</v>
       </c>
       <c r="E4" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F4" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G4" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>2307</v>
+        <v>2299</v>
       </c>
       <c r="K4" t="s">
-        <v>2308</v>
+        <v>2300</v>
       </c>
       <c r="L4" t="s">
-        <v>2307</v>
+        <v>2299</v>
       </c>
       <c r="M4" t="s">
-        <v>2309</v>
+        <v>2301</v>
       </c>
       <c r="N4" t="s">
-        <v>2310</v>
+        <v>2302</v>
       </c>
       <c r="O4"/>
       <c r="P4" t="n">
@@ -16306,33 +16039,33 @@
         <v>499</v>
       </c>
       <c r="E5" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F5" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G5" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>2311</v>
+        <v>2303</v>
       </c>
       <c r="K5" t="s">
-        <v>2312</v>
+        <v>2304</v>
       </c>
       <c r="L5" t="s">
-        <v>2311</v>
+        <v>2303</v>
       </c>
       <c r="M5" t="s">
-        <v>2313</v>
+        <v>2305</v>
       </c>
       <c r="N5" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O5" t="s">
-        <v>2314</v>
+        <v>2306</v>
       </c>
       <c r="P5" t="n">
         <v>346655</v>
@@ -16352,33 +16085,33 @@
         <v>2250</v>
       </c>
       <c r="E6" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F6" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G6" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>2315</v>
+        <v>2307</v>
       </c>
       <c r="K6" t="s">
-        <v>2316</v>
+        <v>2308</v>
       </c>
       <c r="L6" t="s">
-        <v>2315</v>
+        <v>2307</v>
       </c>
       <c r="M6" t="s">
-        <v>2317</v>
+        <v>2309</v>
       </c>
       <c r="N6" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O6" t="s">
-        <v>2318</v>
+        <v>2310</v>
       </c>
       <c r="P6" t="n">
         <v>348244</v>
@@ -16398,33 +16131,33 @@
         <v>825</v>
       </c>
       <c r="E7" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F7" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G7" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>2319</v>
+        <v>2311</v>
       </c>
       <c r="K7" t="s">
-        <v>2320</v>
+        <v>2312</v>
       </c>
       <c r="L7" t="s">
-        <v>2319</v>
+        <v>2311</v>
       </c>
       <c r="M7" t="s">
-        <v>2309</v>
+        <v>2301</v>
       </c>
       <c r="N7" t="s">
-        <v>2310</v>
+        <v>2302</v>
       </c>
       <c r="O7" t="s">
-        <v>2321</v>
+        <v>2313</v>
       </c>
       <c r="P7" t="n">
         <v>350028</v>
@@ -16444,33 +16177,33 @@
         <v>1683</v>
       </c>
       <c r="E8" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F8" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G8" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>2279</v>
+        <v>2271</v>
       </c>
       <c r="K8" t="s">
-        <v>2322</v>
+        <v>2314</v>
       </c>
       <c r="L8" t="s">
-        <v>2279</v>
+        <v>2271</v>
       </c>
       <c r="M8" t="s">
-        <v>2323</v>
+        <v>2315</v>
       </c>
       <c r="N8" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O8" t="s">
-        <v>2281</v>
+        <v>2273</v>
       </c>
       <c r="P8" t="n">
         <v>351457</v>
@@ -16490,33 +16223,33 @@
         <v>2415</v>
       </c>
       <c r="E9" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F9" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G9" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>2282</v>
+        <v>2274</v>
       </c>
       <c r="K9" t="s">
-        <v>2324</v>
+        <v>2316</v>
       </c>
       <c r="L9" t="s">
-        <v>2282</v>
+        <v>2274</v>
       </c>
       <c r="M9" t="s">
-        <v>2325</v>
+        <v>2317</v>
       </c>
       <c r="N9" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O9" t="s">
-        <v>2283</v>
+        <v>2275</v>
       </c>
       <c r="P9" t="n">
         <v>354265</v>
@@ -16536,30 +16269,30 @@
         <v>1146</v>
       </c>
       <c r="E10" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F10" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G10" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>2265</v>
+        <v>2257</v>
       </c>
       <c r="K10" t="s">
-        <v>2326</v>
+        <v>2318</v>
       </c>
       <c r="L10" t="s">
-        <v>2265</v>
+        <v>2257</v>
       </c>
       <c r="M10" t="s">
-        <v>2309</v>
+        <v>2301</v>
       </c>
       <c r="N10" t="s">
-        <v>2310</v>
+        <v>2302</v>
       </c>
       <c r="O10"/>
       <c r="P10" t="n">
@@ -16580,30 +16313,30 @@
         <v>963</v>
       </c>
       <c r="E11" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F11" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G11" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>2327</v>
+        <v>2319</v>
       </c>
       <c r="K11" t="s">
-        <v>2328</v>
+        <v>2320</v>
       </c>
       <c r="L11" t="s">
-        <v>2327</v>
+        <v>2319</v>
       </c>
       <c r="M11" t="s">
-        <v>2309</v>
+        <v>2301</v>
       </c>
       <c r="N11" t="s">
-        <v>2310</v>
+        <v>2302</v>
       </c>
       <c r="O11"/>
       <c r="P11" t="n">
@@ -16624,33 +16357,33 @@
         <v>393</v>
       </c>
       <c r="E12" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F12" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G12" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>2275</v>
+        <v>2267</v>
       </c>
       <c r="K12" t="s">
-        <v>2329</v>
+        <v>2321</v>
       </c>
       <c r="L12" t="s">
-        <v>2275</v>
+        <v>2267</v>
       </c>
       <c r="M12" t="s">
-        <v>2330</v>
+        <v>2322</v>
       </c>
       <c r="N12" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O12" t="s">
-        <v>2276</v>
+        <v>2268</v>
       </c>
       <c r="P12" t="n">
         <v>358832</v>
@@ -16670,33 +16403,33 @@
         <v>657</v>
       </c>
       <c r="E13" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F13" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G13" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>2331</v>
+        <v>2323</v>
       </c>
       <c r="K13" t="s">
-        <v>2332</v>
+        <v>2324</v>
       </c>
       <c r="L13" t="s">
-        <v>2331</v>
+        <v>2323</v>
       </c>
       <c r="M13" t="s">
-        <v>2333</v>
+        <v>2325</v>
       </c>
       <c r="N13" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O13" t="s">
-        <v>2334</v>
+        <v>2326</v>
       </c>
       <c r="P13" t="n">
         <v>359772</v>
@@ -16716,33 +16449,33 @@
         <v>1572</v>
       </c>
       <c r="E14" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F14" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G14" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>2269</v>
+        <v>2261</v>
       </c>
       <c r="K14" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="L14" t="s">
-        <v>2269</v>
+        <v>2261</v>
       </c>
       <c r="M14" t="s">
-        <v>2336</v>
+        <v>2328</v>
       </c>
       <c r="N14" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O14" t="s">
-        <v>2271</v>
+        <v>2263</v>
       </c>
       <c r="P14" t="n">
         <v>361074</v>
@@ -16762,33 +16495,33 @@
         <v>1692</v>
       </c>
       <c r="E15" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F15" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G15" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>2277</v>
+        <v>2269</v>
       </c>
       <c r="K15" t="s">
-        <v>2337</v>
+        <v>2329</v>
       </c>
       <c r="L15" t="s">
-        <v>2277</v>
+        <v>2269</v>
       </c>
       <c r="M15" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="N15" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O15" t="s">
-        <v>2278</v>
+        <v>2270</v>
       </c>
       <c r="P15" t="n">
         <v>363070</v>
@@ -16808,33 +16541,33 @@
         <v>1662</v>
       </c>
       <c r="E16" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F16" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G16" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>2339</v>
+        <v>2331</v>
       </c>
       <c r="K16" t="s">
-        <v>2340</v>
+        <v>2332</v>
       </c>
       <c r="L16" t="s">
-        <v>2339</v>
+        <v>2331</v>
       </c>
       <c r="M16" t="s">
-        <v>2341</v>
+        <v>2333</v>
       </c>
       <c r="N16" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O16" t="s">
-        <v>2342</v>
+        <v>2334</v>
       </c>
       <c r="P16" t="n">
         <v>365166</v>
@@ -16854,33 +16587,33 @@
         <v>1164</v>
       </c>
       <c r="E17" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F17" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G17" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>2343</v>
+        <v>2335</v>
       </c>
       <c r="K17" t="s">
-        <v>2344</v>
+        <v>2336</v>
       </c>
       <c r="L17" t="s">
-        <v>2343</v>
+        <v>2335</v>
       </c>
       <c r="M17" t="s">
-        <v>2345</v>
+        <v>2337</v>
       </c>
       <c r="N17" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O17" t="s">
-        <v>2346</v>
+        <v>2338</v>
       </c>
       <c r="P17" t="n">
         <v>367506</v>
@@ -16900,33 +16633,33 @@
         <v>2502</v>
       </c>
       <c r="E18" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F18" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G18" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>2347</v>
+        <v>2339</v>
       </c>
       <c r="K18" t="s">
-        <v>2348</v>
+        <v>2340</v>
       </c>
       <c r="L18" t="s">
-        <v>2347</v>
+        <v>2339</v>
       </c>
       <c r="M18" t="s">
-        <v>2349</v>
+        <v>2341</v>
       </c>
       <c r="N18" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O18" t="s">
-        <v>2350</v>
+        <v>2342</v>
       </c>
       <c r="P18" t="n">
         <v>370004</v>
@@ -16946,33 +16679,33 @@
         <v>2073</v>
       </c>
       <c r="E19" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F19" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G19" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>2351</v>
+        <v>2343</v>
       </c>
       <c r="K19" t="s">
-        <v>2352</v>
+        <v>2344</v>
       </c>
       <c r="L19" t="s">
-        <v>2351</v>
+        <v>2343</v>
       </c>
       <c r="M19" t="s">
-        <v>2353</v>
+        <v>2345</v>
       </c>
       <c r="N19" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O19" t="s">
-        <v>2354</v>
+        <v>2346</v>
       </c>
       <c r="P19" t="n">
         <v>373048</v>
@@ -16992,33 +16725,33 @@
         <v>369</v>
       </c>
       <c r="E20" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F20" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G20" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>2355</v>
+        <v>2347</v>
       </c>
       <c r="K20" t="s">
-        <v>2356</v>
+        <v>2348</v>
       </c>
       <c r="L20" t="s">
-        <v>2355</v>
+        <v>2347</v>
       </c>
       <c r="M20" t="s">
-        <v>2357</v>
+        <v>2349</v>
       </c>
       <c r="N20" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O20" t="s">
-        <v>2358</v>
+        <v>2350</v>
       </c>
       <c r="P20" t="n">
         <v>374643</v>
@@ -17038,33 +16771,33 @@
         <v>585</v>
       </c>
       <c r="E21" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F21" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G21" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>2359</v>
+        <v>2351</v>
       </c>
       <c r="K21" t="s">
-        <v>2360</v>
+        <v>2352</v>
       </c>
       <c r="L21" t="s">
-        <v>2359</v>
+        <v>2351</v>
       </c>
       <c r="M21" t="s">
-        <v>2361</v>
+        <v>2353</v>
       </c>
       <c r="N21" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O21" t="s">
-        <v>2362</v>
+        <v>2354</v>
       </c>
       <c r="P21" t="n">
         <v>375379</v>
@@ -17084,33 +16817,33 @@
         <v>1155</v>
       </c>
       <c r="E22" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F22" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G22" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>2363</v>
+        <v>2355</v>
       </c>
       <c r="K22" t="s">
-        <v>2364</v>
+        <v>2356</v>
       </c>
       <c r="L22" t="s">
-        <v>2363</v>
+        <v>2355</v>
       </c>
       <c r="M22" t="s">
-        <v>2365</v>
+        <v>2357</v>
       </c>
       <c r="N22" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O22" t="s">
-        <v>2366</v>
+        <v>2358</v>
       </c>
       <c r="P22" t="n">
         <v>376678</v>
@@ -17130,33 +16863,33 @@
         <v>1974</v>
       </c>
       <c r="E23" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F23" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G23" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>2284</v>
+        <v>2276</v>
       </c>
       <c r="K23" t="s">
-        <v>2367</v>
+        <v>2359</v>
       </c>
       <c r="L23" t="s">
-        <v>2284</v>
+        <v>2276</v>
       </c>
       <c r="M23" t="s">
-        <v>2368</v>
+        <v>2360</v>
       </c>
       <c r="N23" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O23" t="s">
-        <v>2286</v>
+        <v>2278</v>
       </c>
       <c r="P23" t="n">
         <v>378596</v>
@@ -17176,33 +16909,33 @@
         <v>1512</v>
       </c>
       <c r="E24" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F24" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G24" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>2272</v>
+        <v>2264</v>
       </c>
       <c r="K24" t="s">
-        <v>2369</v>
+        <v>2361</v>
       </c>
       <c r="L24" t="s">
-        <v>2272</v>
+        <v>2264</v>
       </c>
       <c r="M24" t="s">
-        <v>2370</v>
+        <v>2362</v>
       </c>
       <c r="N24" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O24" t="s">
-        <v>2274</v>
+        <v>2266</v>
       </c>
       <c r="P24" t="n">
         <v>380516</v>
@@ -17222,33 +16955,33 @@
         <v>1686</v>
       </c>
       <c r="E25" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F25" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G25" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>2371</v>
+        <v>2363</v>
       </c>
       <c r="K25" t="s">
-        <v>2372</v>
+        <v>2364</v>
       </c>
       <c r="L25" t="s">
-        <v>2371</v>
+        <v>2363</v>
       </c>
       <c r="M25" t="s">
-        <v>2373</v>
+        <v>2365</v>
       </c>
       <c r="N25" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O25" t="s">
-        <v>2374</v>
+        <v>2366</v>
       </c>
       <c r="P25" t="n">
         <v>382366</v>
@@ -17268,33 +17001,33 @@
         <v>1113</v>
       </c>
       <c r="E26" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F26" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G26" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>2375</v>
+        <v>2367</v>
       </c>
       <c r="K26" t="s">
-        <v>2376</v>
+        <v>2368</v>
       </c>
       <c r="L26" t="s">
-        <v>2375</v>
+        <v>2367</v>
       </c>
       <c r="M26" t="s">
-        <v>2377</v>
+        <v>2369</v>
       </c>
       <c r="N26" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O26" t="s">
-        <v>2378</v>
+        <v>2370</v>
       </c>
       <c r="P26" t="n">
         <v>384210</v>
@@ -17314,33 +17047,33 @@
         <v>3537</v>
       </c>
       <c r="E27" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F27" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G27" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>2379</v>
+        <v>2371</v>
       </c>
       <c r="K27" t="s">
-        <v>2380</v>
+        <v>2372</v>
       </c>
       <c r="L27" t="s">
-        <v>2379</v>
+        <v>2371</v>
       </c>
       <c r="M27" t="s">
-        <v>2381</v>
+        <v>2373</v>
       </c>
       <c r="N27" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O27" t="s">
-        <v>2382</v>
+        <v>2374</v>
       </c>
       <c r="P27" t="n">
         <v>386964</v>
@@ -17360,33 +17093,33 @@
         <v>744</v>
       </c>
       <c r="E28" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F28" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G28" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>2383</v>
+        <v>2375</v>
       </c>
       <c r="K28" t="s">
-        <v>2384</v>
+        <v>2376</v>
       </c>
       <c r="L28" t="s">
-        <v>2383</v>
+        <v>2375</v>
       </c>
       <c r="M28" t="s">
-        <v>2385</v>
+        <v>2377</v>
       </c>
       <c r="N28" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O28" t="s">
-        <v>2386</v>
+        <v>2378</v>
       </c>
       <c r="P28" t="n">
         <v>389340</v>
@@ -17406,33 +17139,33 @@
         <v>1926</v>
       </c>
       <c r="E29" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F29" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G29" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29" t="s">
-        <v>2387</v>
+        <v>2379</v>
       </c>
       <c r="K29" t="s">
-        <v>2388</v>
+        <v>2380</v>
       </c>
       <c r="L29" t="s">
-        <v>2387</v>
+        <v>2379</v>
       </c>
       <c r="M29" t="s">
-        <v>2389</v>
+        <v>2381</v>
       </c>
       <c r="N29" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O29" t="s">
-        <v>2390</v>
+        <v>2382</v>
       </c>
       <c r="P29" t="n">
         <v>391028</v>
@@ -17452,33 +17185,33 @@
         <v>1476</v>
       </c>
       <c r="E30" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F30" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G30" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30" t="s">
-        <v>2266</v>
+        <v>2258</v>
       </c>
       <c r="K30" t="s">
-        <v>2391</v>
+        <v>2383</v>
       </c>
       <c r="L30" t="s">
-        <v>2266</v>
+        <v>2258</v>
       </c>
       <c r="M30" t="s">
-        <v>2392</v>
+        <v>2384</v>
       </c>
       <c r="N30" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O30" t="s">
-        <v>2268</v>
+        <v>2260</v>
       </c>
       <c r="P30" t="n">
         <v>392960</v>
@@ -17498,33 +17231,33 @@
         <v>519</v>
       </c>
       <c r="E31" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="F31" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G31" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31" t="s">
-        <v>2393</v>
+        <v>2385</v>
       </c>
       <c r="K31" t="s">
-        <v>2394</v>
+        <v>2386</v>
       </c>
       <c r="L31" t="s">
-        <v>2393</v>
+        <v>2385</v>
       </c>
       <c r="M31" t="s">
-        <v>2395</v>
+        <v>2387</v>
       </c>
       <c r="N31" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O31" t="s">
-        <v>2396</v>
+        <v>2388</v>
       </c>
       <c r="P31" t="n">
         <v>394245</v>
@@ -17544,33 +17277,33 @@
         <v>864</v>
       </c>
       <c r="E32" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F32" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G32" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" t="s">
-        <v>2262</v>
+        <v>2254</v>
       </c>
       <c r="K32" t="s">
-        <v>2397</v>
+        <v>2389</v>
       </c>
       <c r="L32" t="s">
-        <v>2262</v>
+        <v>2254</v>
       </c>
       <c r="M32" t="s">
-        <v>2398</v>
+        <v>2390</v>
       </c>
       <c r="N32" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O32" t="s">
-        <v>2264</v>
+        <v>2256</v>
       </c>
       <c r="P32" t="n">
         <v>395398</v>
@@ -17590,33 +17323,33 @@
         <v>1584</v>
       </c>
       <c r="E33" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="F33" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="G33" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" t="s">
-        <v>2399</v>
+        <v>2391</v>
       </c>
       <c r="K33" t="s">
-        <v>2400</v>
+        <v>2392</v>
       </c>
       <c r="L33" t="s">
-        <v>2399</v>
+        <v>2391</v>
       </c>
       <c r="M33" t="s">
-        <v>2401</v>
+        <v>2393</v>
       </c>
       <c r="N33" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="O33" t="s">
-        <v>2402</v>
+        <v>2394</v>
       </c>
       <c r="P33" t="n">
         <v>396826</v>
@@ -29241,10 +28974,10 @@
         <v>0.00155044288688888</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0511646152673331</v>
+        <v>0.029334226020911</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0375370383141519</v>
+        <v>0.0215211227585631</v>
       </c>
       <c r="J2" t="s">
         <v>602</v>
@@ -29273,19 +29006,19 @@
         <v>607</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0058658026826746</v>
+        <v>0.00177783188005521</v>
       </c>
       <c r="H3" t="n">
-        <v>0.060093355366872</v>
+        <v>0.029334226020911</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0440876291367801</v>
+        <v>0.0215211227585631</v>
       </c>
       <c r="J3" t="s">
         <v>608</v>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
